--- a/templates/20-five-whys-tree.xlsx
+++ b/templates/20-five-whys-tree.xlsx
@@ -651,7 +651,7 @@
   <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
@@ -781,7 +781,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>1</t>
@@ -824,28 +824,88 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="12" t="n"/>
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>The agent could not see whether the adjustment had posted</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Billing status lives in another system with no view inside the ticket</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>The integration was scoped to write, never to read</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>No one owned the end-to-end lifecycle when it was designed</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>Sample 50 reopens and check whether the agent had visibility at closure</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
-      <c r="H12" s="12" t="n"/>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>We only count reopens raised for the same reason</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>The metric was defined by reporting without asking operations</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>No operational definition was agreed when the project started</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>The organisation has no standard for who signs off a metric definition</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Recount reopens on an any-reason definition and compare the two series</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="5" t="n">

--- a/templates/20-five-whys-tree.xlsx
+++ b/templates/20-five-whys-tree.xlsx
@@ -207,6 +207,31 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Template</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>One concrete record, with it open in front of you: ticket number, what happened, and when. 'Reopens are high' is not an instance and cannot be walked back to a cause.</t>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
+      <text>
+        <t>The date of the instance, not the date you ran the session. You will want to go back to the system state as it was.</t>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0">
+      <text>
+        <t>What the customer experienced, in their terms. Not the internal symptom and not the fix you already have in mind.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1138,5 +1163,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/templates/20-five-whys-tree.xlsx
+++ b/templates/20-five-whys-tree.xlsx
@@ -220,7 +220,7 @@
         <t>One concrete record, with it open in front of you: ticket number, what happened, and when. 'Reopens are high' is not an instance and cannot be walked back to a cause.</t>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0">
+    <comment ref="H5" authorId="0" shapeId="0">
       <text>
         <t>The date of the instance, not the date you ran the session. You will want to go back to the system state as it was.</t>
       </text>
@@ -673,17 +673,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -699,6 +700,7 @@
       <c r="F1" s="4" t="n"/>
       <c r="G1" s="4" t="n"/>
       <c r="H1" s="4" t="n"/>
+      <c r="I1" s="4" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -721,6 +723,7 @@
       <c r="F4" s="7" t="n"/>
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -733,12 +736,12 @@
           <t>Billing ticket #48217, closed 12 Mar, reopened 14 Mar</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
@@ -787,20 +790,25 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>Why 4 / 5</t>
+          <t>Why 4</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
+          <t>Why 5</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
           <t>Branch?</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>Testable with data?</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>How you would test it</t>
         </is>
@@ -824,25 +832,30 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>The status model has no pending state</t>
+          <t>The ticket status model has no 'pending adjustment' state</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Nobody owns the ticket lifecycle across billing and support</t>
+          <t>The billing integration was specified as fire-and-forget, with no callback</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
+          <t>No one owned the ticket lifecycle across billing and support when it was designed</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Count reopens where closure preceded the webhook timestamp</t>
         </is>
@@ -871,20 +884,25 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>No one owned the end-to-end lifecycle when it was designed</t>
+          <t>Scope was cut on integration cost, with no one costing the agent's workflow</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
+          <t>Design reviews do not require sign-off from anyone who works the queue</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>Sample 50 reopens and check whether the agent had visibility at closure</t>
         </is>
@@ -913,20 +931,25 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>The organisation has no standard for who signs off a metric definition</t>
+          <t>The charter template does not require one before the baseline is taken</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
+          <t>Metric definitions have no owner anywhere in the organisation</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>Recount reopens on an any-reason definition and compare the two series</t>
         </is>
@@ -943,6 +966,7 @@
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="n">
@@ -955,6 +979,7 @@
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
+      <c r="I14" s="12" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="5" t="n">
@@ -967,6 +992,7 @@
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
+      <c r="I15" s="12" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="n">
@@ -979,6 +1005,7 @@
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="5" t="n">
@@ -991,6 +1018,7 @@
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="n">
@@ -1003,6 +1031,7 @@
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
+      <c r="I18" s="12" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="5" t="n">
@@ -1015,6 +1044,7 @@
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="5" t="n">
@@ -1027,6 +1057,7 @@
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="5" t="n">
@@ -1039,6 +1070,7 @@
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="5" t="n">
@@ -1051,6 +1083,7 @@
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="12" t="n"/>
       <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="5" t="n">
@@ -1063,6 +1096,7 @@
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="12" t="n"/>
       <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="5" t="n">
@@ -1075,6 +1109,7 @@
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="12" t="n"/>
       <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="5" t="n">
@@ -1087,6 +1122,7 @@
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="12" t="n"/>
       <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -1101,6 +1137,7 @@
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="7" t="n"/>
+      <c r="I27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -1108,7 +1145,7 @@
           <t>Branches explored</t>
         </is>
       </c>
-      <c r="E28" s="13">
+      <c r="F28" s="13">
         <f>COUNTA(B10:B25)</f>
         <v/>
       </c>
@@ -1119,44 +1156,56 @@
           <t>Branches you can test with data</t>
         </is>
       </c>
-      <c r="E29" s="13">
-        <f>COUNTIF(G10:G25,"Yes")</f>
+      <c r="F29" s="13">
+        <f>COUNTIF(H10:H25,"Yes")</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
+          <t>Chains that reached five levels</t>
+        </is>
+      </c>
+      <c r="F30" s="13">
+        <f>COUNTA(F10:F25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
           <t>Chains that stopped at a person</t>
         </is>
       </c>
-      <c r="E30" s="13">
-        <f>COUNTIF(E10:E25,"*training*")+COUNTIF(E10:E25,"*follow*")</f>
+      <c r="F31" s="13">
+        <f>COUNTIF(F10:F25,"*training*")+COUNTIF(F10:F25,"*follow the process*")</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>If your last why is 'not enough training' or 'the agent did not follow the process', you stopped one level too early. Ask why the process was skippable — that is the cause you can actually fix.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A2:H2"/>
+  <mergeCells count="11">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A27:I27"/>
     <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A4:I4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G10:G25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H10:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/templates/20-five-whys-tree.xlsx
+++ b/templates/20-five-whys-tree.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>1</t>
@@ -861,7 +861,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>2</t>
@@ -908,7 +908,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="45" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>3</t>

--- a/templates/20-five-whys-tree.xlsx
+++ b/templates/20-five-whys-tree.xlsx
@@ -1124,6 +1124,7 @@
       <c r="H25" s="12" t="n"/>
       <c r="I25" s="12" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
@@ -1183,6 +1184,7 @@
         <v/>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>

--- a/templates/20-five-whys-tree.xlsx
+++ b/templates/20-five-whys-tree.xlsx
@@ -562,14 +562,14 @@
     <row r="6">
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Green row</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
+          <t>Green cells</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>A worked example so you can see the expected format. Delete it when you start.</t>
+          <t>A worked example, so you can see the expected format and the charts say something the moment you open the file. Replace it with your own data when you start.</t>
         </is>
       </c>
     </row>

--- a/templates/20-five-whys-tree.xlsx
+++ b/templates/20-five-whys-tree.xlsx
@@ -108,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -123,6 +123,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -759,8 +762,8 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="5" t="inlineStr">
+    <row r="7" ht="13" customHeight="1">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Start from a concrete instance with the record in front of you. At each level ask 'what else could cause this?' before you go deeper.</t>
         </is>
@@ -768,188 +771,188 @@
     </row>
     <row r="8"/>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Why 1</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Why 2</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Why 3</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Why 4</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Why 5</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>Branch?</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>Testable with data?</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>How you would test it</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>The adjustment had not posted when the ticket was closed</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>Closure is allowed before the posting webhook confirms</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>The ticket status model has no 'pending adjustment' state</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>The billing integration was specified as fire-and-forget, with no callback</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>No one owned the ticket lifecycle across billing and support when it was designed</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>Count reopens where closure preceded the webhook timestamp</t>
         </is>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>The agent could not see whether the adjustment had posted</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>Billing status lives in another system with no view inside the ticket</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>The integration was scoped to write, never to read</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Scope was cut on integration cost, with no one costing the agent's workflow</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>Design reviews do not require sign-off from anyone who works the queue</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>Sample 50 reopens and check whether the agent had visibility at closure</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>We only count reopens raised for the same reason</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>The metric was defined by reporting without asking operations</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>No operational definition was agreed when the project started</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>The charter template does not require one before the baseline is taken</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>Metric definitions have no owner anywhere in the organisation</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>Recount reopens on an any-reason definition and compare the two series</t>
         </is>
@@ -959,170 +962,170 @@
       <c r="A13" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="12" t="n"/>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
+      <c r="H13" s="13" t="n"/>
+      <c r="I13" s="13" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="12" t="n"/>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="n"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="13" t="n"/>
+      <c r="I14" s="13" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="12" t="n"/>
-      <c r="I15" s="12" t="n"/>
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="13" t="n"/>
+      <c r="I15" s="13" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="12" t="n"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="13" t="n"/>
+      <c r="I16" s="13" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="13" t="n"/>
+      <c r="I17" s="13" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="13" t="n"/>
+      <c r="I18" s="13" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="12" t="n"/>
-      <c r="I19" s="12" t="n"/>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="13" t="n"/>
+      <c r="I19" s="13" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="12" t="n"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="13" t="n"/>
+      <c r="H20" s="13" t="n"/>
+      <c r="I20" s="13" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="12" t="n"/>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="13" t="n"/>
+      <c r="H21" s="13" t="n"/>
+      <c r="I21" s="13" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="12" t="n"/>
-      <c r="I22" s="12" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="13" t="n"/>
+      <c r="H22" s="13" t="n"/>
+      <c r="I22" s="13" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="12" t="n"/>
-      <c r="I23" s="12" t="n"/>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="13" t="n"/>
+      <c r="H23" s="13" t="n"/>
+      <c r="I23" s="13" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="12" t="n"/>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="13" t="n"/>
+      <c r="H24" s="13" t="n"/>
+      <c r="I24" s="13" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="12" t="n"/>
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="13" t="n"/>
+      <c r="H25" s="13" t="n"/>
+      <c r="I25" s="13" t="n"/>
     </row>
     <row r="26"/>
     <row r="27">
@@ -1146,7 +1149,7 @@
           <t>Branches explored</t>
         </is>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="14">
         <f>COUNTA(B10:B25)</f>
         <v/>
       </c>
@@ -1157,7 +1160,7 @@
           <t>Branches you can test with data</t>
         </is>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="14">
         <f>COUNTIF(H10:H25,"Yes")</f>
         <v/>
       </c>
@@ -1168,7 +1171,7 @@
           <t>Chains that reached five levels</t>
         </is>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="14">
         <f>COUNTA(F10:F25)</f>
         <v/>
       </c>
@@ -1179,7 +1182,7 @@
           <t>Chains that stopped at a person</t>
         </is>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="14">
         <f>COUNTIF(F10:F25,"*training*")+COUNTIF(F10:F25,"*follow the process*")</f>
         <v/>
       </c>
@@ -1193,11 +1196,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A33:I33"/>
+    <mergeCell ref="B7:I7"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="A1:I1"/>
